--- a/output/pdf_financials_xlsx/CNRI.xlsx
+++ b/output/pdf_financials_xlsx/CNRI.xlsx
@@ -1779,7 +1779,7 @@
         <v>0.000122</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.553324</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>19.025817</v>
@@ -1841,7 +1841,7 @@
         <v>0.000122</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.553324</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>19.025817</v>
@@ -2213,7 +2213,7 @@
         <v>7e-06</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.553324</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.036219</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">

--- a/output/pdf_financials_xlsx/CNRI.xlsx
+++ b/output/pdf_financials_xlsx/CNRI.xlsx
@@ -3879,10 +3879,10 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.065953</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.09292400000000001</v>
       </c>
       <c r="H100" s="3" t="n">
         <v>0</v>
@@ -12180,7 +12180,11 @@
           <t>Depreciation for property and equipment 4</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CNRI.xlsx
+++ b/output/pdf_financials_xlsx/CNRI.xlsx
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3e-06</v>
+        <v>9.3e-05</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>3e-06</v>
+        <v>0.000101</v>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0.2097902097902098</v>
+        <v>6.503496503496503</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.906344410876133</v>
+        <v>30.51359516616314</v>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>9e-06</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>1.7e-05</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
@@ -2920,10 +2920,10 @@
         <v>0</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.960371</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.83474</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>0</v>
@@ -2951,10 +2951,10 @@
         <v>0</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.960371</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.83474</v>
       </c>
       <c r="I71" s="3" t="n">
         <v>0</v>
@@ -3075,10 +3075,10 @@
         <v>3.082559</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.960371</v>
+        <v>0</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.83474</v>
+        <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0</v>
@@ -3243,15 +3243,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G80" s="3" t="n">
+        <v>0.02134136388988635</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0.01925346097072004</v>
       </c>
       <c r="I80" s="1" t="inlineStr">
         <is>
@@ -3911,19 +3907,19 @@
         <v>0</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.015378</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-1.192587</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.507613</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.51269</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.04257</v>
       </c>
     </row>
     <row r="102">
@@ -4086,19 +4082,19 @@
         <v>0.117158</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.293689</v>
+        <v>-0.278311</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.130907</v>
+        <v>-1.06168</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.316984</v>
+        <v>0.190629</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.006921</v>
+        <v>0.519611</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.494963</v>
+        <v>0.537533</v>
       </c>
     </row>
     <row r="107">
@@ -5742,7 +5738,11 @@
           <t>Current portion of lease obligations 8</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -11058,7 +11058,11 @@
           <t>Deferred tax expense (recovery) 11</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -11268,7 +11272,11 @@
           <t>Prepaid expenses and HST receivable</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -11422,7 +11430,11 @@
           <t>Proceeds from share issuance 7</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -12352,7 +12364,11 @@
           <t>Deferred tax expenses 12</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -14414,7 +14430,11 @@
           <t>Future income tax recovery (Note 13)</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E171" s="5" t="n">
         <v>-9.3e-05</v>
       </c>
